--- a/ML_models/component02/data/hikingsources.xlsx
+++ b/ML_models/component02/data/hikingsources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61C09AA-94B4-461A-ADE6-7D50557B0C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C3B302-F837-40D7-A343-C5070FA524AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A4508BA2-F452-4668-95F8-2502E0722D23}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="143">
   <si>
     <t>record_id</t>
   </si>
@@ -325,6 +325,171 @@
   <si>
     <t xml:space="preserve">Alltrails: A really tough climb of 200m due to the heat and humidity. Best to climb early morning as the midday sun is scorching. A good level of fitness is required due to the 1200 plus steps some of which are very narrow and steep. Tips: An umbrella is handy for welcome shade when resting and taking in the views as the heat can be intense. Wear a good pair of trainers with grip to support your ankles and prevent slipping on gravelly areas. Be aware of the steep $30 charge per tourist to climb the rock and note that this place can be very overcrowded. We climbed the rock early March 2020. Great views at the top!
 </t>
+  </si>
+  <si>
+    <t>Alltrails: Handy to have all trails downloaded as there are several trails that take you in different directions, so would be easy to get lost. Have to pay entry at the top (not expensive) Conditions: Bugs, Dry ground, Overgrown Parking: Entry fee Difficulty: Moderate</t>
+  </si>
+  <si>
+    <t>Alltrails: Don’t follow the exit signs, they take you to the middle of the woods so that can farmers can help you and charge you after. We had to go through a field full of leeches.</t>
+  </si>
+  <si>
+    <t>Ella rock</t>
+  </si>
+  <si>
+    <t>2026.09.16</t>
+  </si>
+  <si>
+    <t>2026.10.09</t>
+  </si>
+  <si>
+    <t>Alltrails: The trail winds past water sources and tea fields. It’s pretty open, and we didn’t run into any leeches! Just follow the trail closely, and you’ll be fine. A nice reward at the end!</t>
+  </si>
+  <si>
+    <t>2026.08.27</t>
+  </si>
+  <si>
+    <t>2026.02.25</t>
+  </si>
+  <si>
+    <t>2026.07.31</t>
+  </si>
+  <si>
+    <t>Alltrails: Nice and easy walk (quite steep though before the top but it’s short), easy to find the way if you follow AllTrails trace. We met nobody trying to accompany us, as mentioned by other travellers. The weather was dry, so no leeches, no mosquitos. The view at the top is nice, but nothing so special. If you don’t want to pay the fee at the top, you can turn right to join the 2nd view point (on our side, we considered it’s part of the “game”)</t>
+  </si>
+  <si>
+    <t>Alltrails: Started at 430pm, ended around 7pm including time for viewpoints at the top. Hike is moderate, definitely not hard. Flat at the start and steep 300m or so section in the middle. Follow the trail here closely, easy to miss turns as there are many other possible routes in the tea plantations. Especially the 1st left turn right after the bridge which can be unassuming. Views were excellent, only saw 1 other group on the entire trail. No leeches encountered.</t>
+  </si>
+  <si>
+    <t>2026.05.30</t>
+  </si>
+  <si>
+    <t>Got a bit lost on the way back from Ella rock😆😆😆 covered in leeches. So funny</t>
+  </si>
+  <si>
+    <t>2026.05.24</t>
+  </si>
+  <si>
+    <t>All trails: It’s pretty steep by the end and I needed to catch my breath every 5minutes but completely worth it. Going down is also hard on the knees and a little slippery when too steep. So be careful.</t>
+  </si>
+  <si>
+    <t>2026.03.07</t>
+  </si>
+  <si>
+    <t>Alltrails: We started at the Escapade Hostel - arrive early so the road there doesn’t get too busy. We were there 0830-0900 which was fine. It was a steady climb all the to the top but manageable. I don’t like heights and I was fine. I would not recommended doing it in the rain unless you are sure footed because there are plenty of slippy spots. Decent trainers are a must! 930 rupee entry fee at top to access the view points. We were told to wear long trousers in case of leeches !</t>
+  </si>
+  <si>
+    <t>Alltrails: Big hike. Keep an eye on the GPS because it is easy to get lost.</t>
+  </si>
+  <si>
+    <t>2026.01.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alltrails: Leeches
+Conditions: Bugs, Muddy, Overgrown
+</t>
+  </si>
+  <si>
+    <t>2025.12.19</t>
+  </si>
+  <si>
+    <t>Alltrails: If it’s raining and due to rain all day, it’s very unlikely to have any visibility. Remember it’ll get dark earlier than sunset if cloudy.</t>
+  </si>
+  <si>
+    <t>2025.11.26</t>
+  </si>
+  <si>
+    <t>2025.11.22</t>
+  </si>
+  <si>
+    <t>A great, easy to follow trail going through lots of lush landscape. We were in a cloud at the top so were not able to see the view, but still very worth it! Do note that at the beginning after the bridge this trail tells you to make a hard left, but ignore that and continue walking for 10 metres or so and there will be a better maintained path to the left through the tea plantations! If you’ve done Little Adam’s Peak you can certainly do this trail, it isn’t challenging just very steep! It was raining when we did it so the leeches did come out so beware!. Conditions: Muddy</t>
+  </si>
+  <si>
+    <t>Alltrails: Stick to the road on the app, There is a lot of other roads and it easy to confuse. Also there is a lot of Sri Lanka people that trying to walk we you to the top for some money, you only need to stick the marked road on the app and you’re going to be very fine. Conditions: Bugs, Muddy, Overgrown, Dusty, Poor air quality, Poisonous plants, Wildflowers</t>
+  </si>
+  <si>
+    <t>2025.11.10</t>
+  </si>
+  <si>
+    <t>Alltrails: Beautiful walk. Read the reviews about not getting scammed. Still almost got sucked in when locals told us we were going the wrong way and put sticks/barriers over the path. Follow the All Trails map at all costs and you will be fine. Conditions: Bugs, Muddy, Obstructions</t>
+  </si>
+  <si>
+    <t>2025.04.18</t>
+  </si>
+  <si>
+    <t>2025.04.02</t>
+  </si>
+  <si>
+    <t>Alltrails: Don’t go this way - involves going through a house with a very aggressive looking dog + leeches!</t>
+  </si>
+  <si>
+    <t>Alltrails: The day I went was mostly overcast and drizzly so the views were not great. Otherwise it was a nice hike though tea plantations and the forest. The hike along the train tracks was also cool. I followed others comments about going counterclockwise to avoid paying unnecessary fees</t>
+  </si>
+  <si>
+    <t>2025.02.09</t>
+  </si>
+  <si>
+    <t>Alltrails: Great track. We arrived an hour before sunrise. It was very windy so a warm layer and a windbreaker is a good idea if we want to fully enjoy the special atmosphere before dawn. A dry route with no leeches or bugs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alltrails: Very nice route, tough climb at times. Beware of leeches. Conditions: Bugs
+</t>
+  </si>
+  <si>
+    <t>2024.12.05</t>
+  </si>
+  <si>
+    <t>Alltrails: Route up is fairly simple in the dark. At the turning off the tracks just keep left all the way up. It may seem like it's asking you to go on an unclear trail, but if you just take a look around you should be able to find a more obvious route. There's stones marked with orange paint to show you're on track. We took a different route on the way down to avoid walking the same route down, but as we got closer to the train tracks the route became much less obvious. Walked through a farm and over the river to get back. The trails marked towards the end are far less obvious. I wouldn't recommend the second half of the return trail due to unclear paths and an abundance of leeches. I would suggest looping back into the path you took on the ascent. Conditions: Bugs, Overgrown</t>
+  </si>
+  <si>
+    <t>2024.11.27</t>
+  </si>
+  <si>
+    <t>Alltrails: Lots of leechesConditions: Bugs, Muddy</t>
+  </si>
+  <si>
+    <t>Alltrails: Alternative route to Ella Rock, Sri Lanka. From Ella Breeze Homestay. Easy climb, gentle long slopes. It permits to avoid the stupid fee at the top. Long pants and high socks. Leech everywhere during the rainy season.</t>
+  </si>
+  <si>
+    <t>2024.10.28</t>
+  </si>
+  <si>
+    <t>Alltrails: We got lost a couple of times. The view is lovely and the hike up isn’t too bad if you’re on the right path. Going down we took a different path and we got horrible lost. We were covered in leeches. Luckily a farmer came to our rescue and walked with us until we got the train tracks. The path isn’t really clear and you can get lost easily. Wear high socks!</t>
+  </si>
+  <si>
+    <t>2024.10.14</t>
+  </si>
+  <si>
+    <t>Easy/moderate hike. We saw a glimpse of the view however due to cloud/fog cover, it was limited. To summit all up, it was a great hike.</t>
+  </si>
+  <si>
+    <t>2024.10.11</t>
+  </si>
+  <si>
+    <t>Adam's peak</t>
+  </si>
+  <si>
+    <t>Alltrails: A nice hike, starting at night (we set out at 2:30 a.m. to reach the summit three hours later and catch the sunrise! We were out of luck that day, though, as the fog blocked any view of the beautiful scenery... We made the return trip in 2 hours and 15 minutes, and were able to see some lovely waterfalls that hadn’t been visible at night)</t>
+  </si>
+  <si>
+    <t>2026.07.29</t>
+  </si>
+  <si>
+    <t>2026.05.27</t>
+  </si>
+  <si>
+    <t>2026.05.22</t>
+  </si>
+  <si>
+    <t>Alltrails: A tough route, with rain the whole time. I recommend not going in May anymore.</t>
+  </si>
+  <si>
+    <t>2025.08.16</t>
+  </si>
+  <si>
+    <t>All trails: On my day there was a bit of rain about</t>
+  </si>
+  <si>
+    <t>Alltrails: Went on a rainy, misty day. Knew we’d just be in a cloud the whole time, which we were, but it was still nice. Started at 2:30 am per the guidance of our hotel host, but that was waaaaay too early of a start to catch the 6am sunrise. We tried to slow our steps to extend the hike but still arrived at the top by 5 and had to wait shivering in the cold for an hour. Thankfully a tea could be purchased for 200rp. Total time moving was 3h 33 min, 6.78 miles, 3,376 elevation gain. Really enjoyed the hike and the quiet of the off-season early morning.</t>
   </si>
 </sst>
 </file>
@@ -699,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{238B038B-1A73-451D-9EC4-050CB9DB78C3}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.109375" customWidth="1"/>
@@ -1281,6 +1446,398 @@
         <v>88</v>
       </c>
     </row>
+    <row r="42" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
